--- a/Projects/Pistons_Team_Data.xlsx
+++ b/Projects/Pistons_Team_Data.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Assignments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCD09B4-7B1E-C549-A1B1-8AE541788EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A24F17-728E-494F-831A-56932F440C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14380" yWindow="680" windowWidth="14420" windowHeight="16160" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17540" activeTab="4" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="6" r:id="rId1"/>
     <sheet name="URLs" sheetId="5" r:id="rId2"/>
-    <sheet name="Team Stats" sheetId="1" r:id="rId3"/>
+    <sheet name="Total Team Stats" sheetId="1" r:id="rId3"/>
     <sheet name="Team Rankings" sheetId="3" r:id="rId4"/>
     <sheet name="Team Misc" sheetId="7" r:id="rId5"/>
     <sheet name="Team Misc Rankings" sheetId="8" r:id="rId6"/>

--- a/Projects/Pistons_Team_Data.xlsx
+++ b/Projects/Pistons_Team_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A24F17-728E-494F-831A-56932F440C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57A8B7D-9AA7-4945-8D2A-BC9C5135497E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17540" activeTab="4" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17540" firstSheet="1" activeTab="9" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="6" r:id="rId1"/>
@@ -942,7 +942,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1362,14 +1362,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89043632-EAEA-C843-A274-F34874309775}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="132.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>93</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563C5605-1F6D-5947-9020-A1E2D1AD6860}">
   <dimension ref="A1:AW89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -1553,7 +1553,7 @@
     <col min="49" max="49" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:49">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>174</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:49">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>175</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:49">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:49">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>177</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:49">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:49">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>179</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:49">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>181</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:49">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>182</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:49">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>183</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:49">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>184</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>185</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:49">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>186</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:49">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>187</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:49">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>188</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:49">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>189</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:49">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:49">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>191</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:49">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>192</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:49">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>193</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>194</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:49">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>195</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>196</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:49">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>198</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:49">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>199</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:49">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>200</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:49">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>201</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:49">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>202</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:49">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>203</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:49">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>204</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:49">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:49">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>206</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:49">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:49">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:49">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>209</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:49">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>210</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:49">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:49">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>212</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:49">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>213</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:49">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>214</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:49">
+    <row r="42" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>215</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:49">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>216</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:49">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>217</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:49">
+    <row r="45" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>218</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:49">
+    <row r="46" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>219</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:49">
+    <row r="47" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>220</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:49">
+    <row r="48" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>221</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:49">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>222</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:49">
+    <row r="50" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:49">
+    <row r="51" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>224</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:49">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>225</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:49">
+    <row r="53" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>226</v>
       </c>
@@ -9450,7 +9450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:49">
+    <row r="54" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>227</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:49">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:49">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>229</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:49">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:49">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>231</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:49">
+    <row r="59" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>232</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:49">
+    <row r="60" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>233</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:49">
+    <row r="61" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>234</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:49">
+    <row r="62" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>235</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:49">
+    <row r="63" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>236</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:49">
+    <row r="64" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>237</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:49">
+    <row r="65" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>238</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:49">
+    <row r="66" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>239</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:49">
+    <row r="67" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>240</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:49">
+    <row r="68" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>241</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:49">
+    <row r="69" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>242</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:49">
+    <row r="70" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>243</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:49">
+    <row r="71" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>244</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:49">
+    <row r="72" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>245</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:49">
+    <row r="73" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>246</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:49">
+    <row r="74" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>247</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:49">
+    <row r="75" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:49">
+    <row r="76" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>249</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:49">
+    <row r="77" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>250</v>
       </c>
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:49">
+    <row r="78" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>251</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:49">
+    <row r="79" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>252</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:49">
+    <row r="80" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>253</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:49">
+    <row r="81" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>254</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:49">
+    <row r="82" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>255</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:49">
+    <row r="83" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>256</v>
       </c>
@@ -13920,7 +13920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:49">
+    <row r="84" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>257</v>
       </c>
@@ -14069,7 +14069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:49">
+    <row r="85" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>258</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:49">
+    <row r="86" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>259</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:49">
+    <row r="87" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>260</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:49">
+    <row r="88" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>261</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:49">
+    <row r="89" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -14823,14 +14823,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1331B768-31E2-5249-9BC7-FA3A13F60679}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
     <col min="2" max="2" width="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -14902,7 +14902,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -14979,7 +14979,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -14990,7 +14990,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -15001,7 +15001,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -15034,7 +15034,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -15045,7 +15045,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -15141,7 +15141,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -15149,102 +15149,102 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>1979</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>1978</v>
       </c>
@@ -15314,7 +15314,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8BF652-20B1-7F43-A744-DD05AF1BCB1B}">
   <dimension ref="A1:Z47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -15335,7 +15335,7 @@
     <col min="27" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15415,7 +15415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>9471</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>9010</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>9045</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>8596</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -15815,7 +15815,7 @@
         <v>7676</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>7078</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>8778</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -16055,7 +16055,7 @@
         <v>8509</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>8309</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -16215,7 +16215,7 @@
         <v>8361</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>8077</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>8286</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -16455,7 +16455,7 @@
         <v>7778</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -16535,7 +16535,7 @@
         <v>5997</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>7951</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>7709</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -16775,7 +16775,7 @@
         <v>7727</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>7992</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -16935,7 +16935,7 @@
         <v>7872</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -17015,7 +17015,7 @@
         <v>7941</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>7653</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -17175,7 +17175,7 @@
         <v>7388</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>7492</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -17335,7 +17335,7 @@
         <v>7735</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -17415,7 +17415,7 @@
         <v>7837</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -17495,7 +17495,7 @@
         <v>8483</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>4518</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -17655,92 +17655,92 @@
         <v>7721</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -17756,7 +17756,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD28A50-40A3-544F-91EF-435ACD57F473}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -17783,7 +17783,7 @@
     <col min="24" max="24" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17857,7 +17857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -18005,7 +18005,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -18079,7 +18079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -18227,7 +18227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -18375,7 +18375,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -18523,7 +18523,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -18671,7 +18671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -18745,7 +18745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -18819,7 +18819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -18967,7 +18967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -19115,7 +19115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -19189,7 +19189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -19337,7 +19337,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -19411,7 +19411,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -19485,7 +19485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -19559,7 +19559,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -19633,7 +19633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -19707,7 +19707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -19781,7 +19781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -19855,7 +19855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -19929,92 +19929,92 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -20030,7 +20030,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCAAC25-95FB-A948-83BE-8ACB793BD628}">
   <dimension ref="A1:W47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="3.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -20053,7 +20053,7 @@
     <col min="24" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -20195,7 +20195,7 @@
         <v>781929</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -20266,7 +20266,7 @@
         <v>726378</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>759715</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -20408,7 +20408,7 @@
         <v>663556</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -20479,7 +20479,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -20550,7 +20550,7 @@
         <v>509469</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -20621,7 +20621,7 @@
         <v>675963</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -20692,7 +20692,7 @@
         <v>713945</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -20763,7 +20763,7 @@
         <v>655141</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>677138</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -20905,7 +20905,7 @@
         <v>625917</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>616005</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -21047,7 +21047,7 @@
         <v>606094</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -21118,7 +21118,7 @@
         <v>475638</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -21189,7 +21189,7 @@
         <v>683080</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -21260,7 +21260,7 @@
         <v>768826</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -21331,7 +21331,7 @@
         <v>896971</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>905116</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -21473,7 +21473,7 @@
         <v>905116</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -21544,7 +21544,7 @@
         <v>905116</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -21615,7 +21615,7 @@
         <v>905116</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -21686,7 +21686,7 @@
         <v>872902</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>839278</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>760807</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>607323</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>678470</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -22041,7 +22041,7 @@
         <v>444585</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -22112,92 +22112,92 @@
         <v>794567</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -22210,7 +22210,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37197CD5-75AC-DA40-B0F7-4622002C6CD5}">
   <dimension ref="A1:W47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="3.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -22236,7 +22236,7 @@
     <col min="24" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -22307,7 +22307,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -22378,7 +22378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -22449,7 +22449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -22520,7 +22520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -22591,7 +22591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -22662,7 +22662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -22733,7 +22733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -22875,7 +22875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -22946,7 +22946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -23017,7 +23017,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -23159,7 +23159,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -23230,7 +23230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -23301,7 +23301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -23372,7 +23372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -23443,7 +23443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -23514,7 +23514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -23585,7 +23585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -23798,7 +23798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -23869,7 +23869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -24011,7 +24011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -24082,7 +24082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -24153,7 +24153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -24224,7 +24224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -24295,92 +24295,92 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -24393,7 +24393,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063A38B8-9C5D-914A-9808-4E19C0063B8D}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -24412,7 +24412,7 @@
     <col min="22" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24486,7 +24486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -24560,7 +24560,7 @@
         <v>9315</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -24634,7 +24634,7 @@
         <v>9757</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -24708,7 +24708,7 @@
         <v>9719</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -24782,7 +24782,7 @@
         <v>9229</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>7998</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -24930,7 +24930,7 @@
         <v>7313</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -25004,7 +25004,7 @@
         <v>8798</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>8521</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -25152,7 +25152,7 @@
         <v>8401</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -25226,7 +25226,7 @@
         <v>8311</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -25300,7 +25300,7 @@
         <v>8159</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -25374,7 +25374,7 @@
         <v>8586</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -25448,7 +25448,7 @@
         <v>8105</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -25522,7 +25522,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -25596,7 +25596,7 @@
         <v>8246</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -25670,7 +25670,7 @@
         <v>8128</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -25744,7 +25744,7 @@
         <v>7767</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -25818,7 +25818,7 @@
         <v>7386</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -25892,7 +25892,7 @@
         <v>7531</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -25966,7 +25966,7 @@
         <v>7394</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -26040,7 +26040,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -26114,7 +26114,7 @@
         <v>6909</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -26262,7 +26262,7 @@
         <v>7560</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -26336,7 +26336,7 @@
         <v>7976</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -26410,7 +26410,7 @@
         <v>8365</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -26484,7 +26484,7 @@
         <v>4347</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -26558,92 +26558,92 @@
         <v>7592</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -26659,7 +26659,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B551084D-B439-D643-905D-6D7981519C9A}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -26686,7 +26686,7 @@
     <col min="24" max="24" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26760,7 +26760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2025</v>
       </c>
@@ -26834,7 +26834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2024</v>
       </c>
@@ -26908,7 +26908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2023</v>
       </c>
@@ -26982,7 +26982,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -27056,7 +27056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2021</v>
       </c>
@@ -27130,7 +27130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2020</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2019</v>
       </c>
@@ -27278,7 +27278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2018</v>
       </c>
@@ -27352,7 +27352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2017</v>
       </c>
@@ -27426,7 +27426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2016</v>
       </c>
@@ -27500,7 +27500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2015</v>
       </c>
@@ -27574,7 +27574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2014</v>
       </c>
@@ -27648,7 +27648,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2013</v>
       </c>
@@ -27722,7 +27722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2012</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2011</v>
       </c>
@@ -27870,7 +27870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2010</v>
       </c>
@@ -27944,7 +27944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2009</v>
       </c>
@@ -28018,7 +28018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2008</v>
       </c>
@@ -28092,7 +28092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2007</v>
       </c>
@@ -28166,7 +28166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2006</v>
       </c>
@@ -28240,7 +28240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2005</v>
       </c>
@@ -28314,7 +28314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2004</v>
       </c>
@@ -28388,7 +28388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -28462,7 +28462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2002</v>
       </c>
@@ -28536,7 +28536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2001</v>
       </c>
@@ -28610,7 +28610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2000</v>
       </c>
@@ -28684,7 +28684,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>1999</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>1998</v>
       </c>
@@ -28832,92 +28832,92 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1980</v>
       </c>
@@ -28933,7 +28933,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4B4210-6FED-5146-8608-36FA87CD36EC}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.1640625" style="7" bestFit="1" customWidth="1"/>
@@ -28953,7 +28953,7 @@
     <col min="25" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -29027,7 +29027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2025</v>
       </c>
@@ -29101,7 +29101,7 @@
         <v>9334</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2024</v>
       </c>
@@ -29175,7 +29175,7 @@
         <v>9365</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2023</v>
       </c>
@@ -29249,7 +29249,7 @@
         <v>9404</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>2022</v>
       </c>
@@ -29323,7 +29323,7 @@
         <v>9071</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2021</v>
       </c>
@@ -29397,7 +29397,7 @@
         <v>8071</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>2020</v>
       </c>
@@ -29471,7 +29471,7 @@
         <v>7893</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2019</v>
       </c>
@@ -29545,7 +29545,7 @@
         <v>9119</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>2018</v>
       </c>
@@ -29619,7 +29619,7 @@
         <v>8719</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>2017</v>
       </c>
@@ -29693,7 +29693,7 @@
         <v>8658</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>2016</v>
       </c>
@@ -29767,7 +29767,7 @@
         <v>8419</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2015</v>
       </c>
@@ -29841,7 +29841,7 @@
         <v>8201</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>2014</v>
       </c>
@@ -29915,7 +29915,7 @@
         <v>8283</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>2013</v>
       </c>
@@ -29989,7 +29989,7 @@
         <v>8041</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>2012</v>
       </c>
@@ -30063,7 +30063,7 @@
         <v>6353</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>2011</v>
       </c>
@@ -30137,7 +30137,7 @@
         <v>8163</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>2010</v>
       </c>
@@ -30211,7 +30211,7 @@
         <v>8237</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>2009</v>
       </c>
@@ -30285,7 +30285,7 @@
         <v>8196</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>2008</v>
       </c>
@@ -30359,7 +30359,7 @@
         <v>8194</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2007</v>
       </c>
@@ -30433,7 +30433,7 @@
         <v>8097</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>2006</v>
       </c>
@@ -30507,7 +30507,7 @@
         <v>7955</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>2005</v>
       </c>
@@ -30581,7 +30581,7 @@
         <v>7970</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>2004</v>
       </c>
@@ -30655,7 +30655,7 @@
         <v>7659</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>2003</v>
       </c>
@@ -30729,7 +30729,7 @@
         <v>7797</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>2002</v>
       </c>
@@ -30803,7 +30803,7 @@
         <v>7829</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>2001</v>
       </c>
@@ -30877,7 +30877,7 @@
         <v>7774</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>2000</v>
       </c>
@@ -30951,102 +30951,102 @@
         <v>7993</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>1999</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>1998</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>1997</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>1996</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>1995</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>1994</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>1993</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>1992</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>1990</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>1989</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>1987</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>1986</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>1985</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>1984</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>1983</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>1982</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>1981</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>1980</v>
       </c>

--- a/Projects/Pistons_Team_Data.xlsx
+++ b/Projects/Pistons_Team_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA4C440-058E-7A48-8B72-32333EBF812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC9ADDC-3AD7-CB49-A249-814AF0A56FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41940" yWindow="2880" windowWidth="20160" windowHeight="17540" firstSheet="8" activeTab="11" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
+    <workbookView xWindow="49420" yWindow="600" windowWidth="19220" windowHeight="21000" firstSheet="5" activeTab="9" xr2:uid="{C4F023D4-5F40-4743-811E-DDD7ADE52157}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="6" r:id="rId1"/>
